--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{44487CD0-BD13-6041-A5F9-159EFCAE9298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC819C8-833B-8A4D-A86F-35B7D4F570C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960"/>
+    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="talks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>title</t>
   </si>
@@ -46,9 +46,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post. Yay markdown!</t>
-  </si>
-  <si>
     <t>Poster</t>
   </si>
   <si>
@@ -61,13 +58,19 @@
     <t>Ludwig Maximilian University of Munich</t>
   </si>
   <si>
-    <t>Virtual</t>
+    <t>comet-delivery-poster-munich</t>
+  </si>
+  <si>
+    <t>Munich, DE</t>
+  </si>
+  <si>
+    <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post. Attended virtually.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -909,7 +912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -941,16 +944,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="1">
         <v>45098</v>
@@ -959,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC819C8-833B-8A4D-A86F-35B7D4F570C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B7B98C-2155-6F4A-9735-D90F127F4334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,13 +58,13 @@
     <t>Ludwig Maximilian University of Munich</t>
   </si>
   <si>
-    <t>comet-delivery-poster-munich</t>
-  </si>
-  <si>
     <t>Munich, DE</t>
   </si>
   <si>
     <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post. Attended virtually.</t>
+  </si>
+  <si>
+    <t>http://richard17a.github.io/files/Comet_delivery_poster.pdf</t>
   </si>
 </sst>
 </file>
@@ -959,13 +959,13 @@
         <v>45098</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B7B98C-2155-6F4A-9735-D90F127F4334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1102FD0-09A3-464D-AC5F-7E975719891C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t>comet-delivery-poster</t>
   </si>
   <si>
-    <t>Ludwig Maximilian University of Munich</t>
-  </si>
-  <si>
     <t>Munich, DE</t>
   </si>
   <si>
@@ -65,6 +62,9 @@
   </si>
   <si>
     <t>http://richard17a.github.io/files/Comet_delivery_poster.pdf</t>
+  </si>
+  <si>
+    <t>[Molecular Origins of Life 2023](https://indico.physik.uni-muenchen.de/event/194/)</t>
   </si>
 </sst>
 </file>
@@ -953,19 +953,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1">
         <v>45098</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1102FD0-09A3-464D-AC5F-7E975719891C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A702711-7B0A-9D4D-850E-D7760BD76002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>title</t>
   </si>
@@ -55,6 +55,9 @@
     <t>comet-delivery-poster</t>
   </si>
   <si>
+    <t>Ludwig Maximilian University of Munich</t>
+  </si>
+  <si>
     <t>Munich, DE</t>
   </si>
   <si>
@@ -64,7 +67,10 @@
     <t>http://richard17a.github.io/files/Comet_delivery_poster.pdf</t>
   </si>
   <si>
-    <t>[Molecular Origins of Life 2023](https://indico.physik.uni-muenchen.de/event/194/)</t>
+    <t>conf_url</t>
+  </si>
+  <si>
+    <t>https://indico.physik.uni-muenchen.de/event/194/</t>
   </si>
 </sst>
 </file>
@@ -913,10 +919,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -927,22 +933,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -952,20 +961,23 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1">
+        <v>45098</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1">
-        <v>45098</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A702711-7B0A-9D4D-850E-D7760BD76002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0A12F5-5713-4E41-AA5A-AAF70B8320AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>title</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>https://indico.physik.uni-muenchen.de/event/194/</t>
+  </si>
+  <si>
+    <t>conf_name</t>
+  </si>
+  <si>
+    <t>Molecular Origins of Life, Munich 2023</t>
   </si>
 </sst>
 </file>
@@ -919,10 +925,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -933,25 +939,28 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
+      <c r="J1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -961,23 +970,26 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45098</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1">
-        <v>45098</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0A12F5-5713-4E41-AA5A-AAF70B8320AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E46463-CA0A-C145-989A-AE6E5EAB0749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>title</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Munich, DE</t>
   </si>
   <si>
-    <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post. Attended virtually.</t>
-  </si>
-  <si>
     <t>http://richard17a.github.io/files/Comet_delivery_poster.pdf</t>
   </si>
   <si>
@@ -77,6 +74,15 @@
   </si>
   <si>
     <t>Molecular Origins of Life, Munich 2023</t>
+  </si>
+  <si>
+    <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post.</t>
+  </si>
+  <si>
+    <t>virtual</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -925,71 +931,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
       <c r="J1" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>45098</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E46463-CA0A-C145-989A-AE6E5EAB0749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942A82B8-BAA2-AA4B-B4DC-F8E95C0B8A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>title</t>
   </si>
@@ -77,12 +77,6 @@
   </si>
   <si>
     <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post.</t>
-  </si>
-  <si>
-    <t>virtual</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -931,76 +925,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1">
+      <c r="E2" s="1">
         <v>45098</v>
       </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
     </row>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942A82B8-BAA2-AA4B-B4DC-F8E95C0B8A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27B3202-8CC1-744B-A018-D9C1AA53B313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>title</t>
   </si>
@@ -76,7 +76,28 @@
     <t>Molecular Origins of Life, Munich 2023</t>
   </si>
   <si>
-    <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post.</t>
+    <t>Talk</t>
+  </si>
+  <si>
+    <t>University College London</t>
+  </si>
+  <si>
+    <t>London, UK</t>
+  </si>
+  <si>
+    <t>poster description</t>
+  </si>
+  <si>
+    <t>I presented the recent work investigating the cometary delivery of prebiotic molecules to rocky exoplanets, specifically to understand if this is possible around M dwarf stars.</t>
+  </si>
+  <si>
+    <t>UKEXOM 2023</t>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/ukexom2023</t>
+  </si>
+  <si>
+    <t>comet-delivery-ukexom23</t>
   </si>
 </sst>
 </file>
@@ -925,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -983,13 +1004,42 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45146</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
